--- a/nvidia/model.xlsx
+++ b/nvidia/model.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1023,11 +1023,21 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>Preferred stock</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
           <t>Spot price</t>
         </is>
       </c>
-      <c r="B37" s="10" t="n">
-        <v>211.94</v>
+      <c r="B38" s="10" t="n">
+        <v>218.99</v>
       </c>
     </row>
   </sheetData>
@@ -1523,7 +1533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2105,77 +2115,88 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Equity value</t>
+          <t>- Preferred stock</t>
         </is>
       </c>
       <c r="B27" s="11">
-        <f>B22+B23+B24+B25+B26</f>
+        <f>-Drivers!$B$37</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B28" s="18">
-        <f>B27/Drivers!$B$32</f>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B28" s="11">
+        <f>B22+B23+B24+B25+B26+B27</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Spot price</t>
-        </is>
-      </c>
-      <c r="B29" s="19">
-        <f>Drivers!$B$37</f>
+          <t>Value per share</t>
+        </is>
+      </c>
+      <c r="B29" s="18">
+        <f>B28/Drivers!$B$32</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B30" s="13">
-        <f>B28/B29-1</f>
+          <t>Spot price</t>
+        </is>
+      </c>
+      <c r="B30" s="19">
+        <f>Drivers!$B$38</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>Upside / (downside)</t>
+        </is>
+      </c>
+      <c r="B31" s="13">
+        <f>B29/B30-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
           <t>Terminal value % of EV</t>
         </is>
       </c>
-      <c r="B31" s="13">
+      <c r="B32" s="13">
         <f>B21/B22</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Sanity check: WACC minus terminal growth should exceed 150bp.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>WACC - g</t>
         </is>
       </c>
-      <c r="B34" s="20">
+      <c r="B35" s="20">
         <f>Drivers!$B$30-Drivers!$B$31</f>
         <v/>
       </c>
-      <c r="C34">
-        <f>IF(B34&gt;0.015,"OK","FAIL — terminal value unstable")</f>
+      <c r="C35">
+        <f>IF(B35&gt;0.015,"OK","FAIL — terminal value unstable")</f>
         <v/>
       </c>
     </row>
@@ -2467,7 +2488,7 @@
         <v>0.25</v>
       </c>
       <c r="D4" s="13">
-        <f>B4/Valuation!B29-1</f>
+        <f>B4/Valuation!B30-1</f>
         <v/>
       </c>
       <c r="E4" t="inlineStr">
@@ -2489,7 +2510,7 @@
         <v>0.5</v>
       </c>
       <c r="D5" s="13">
-        <f>B5/Valuation!B29-1</f>
+        <f>B5/Valuation!B30-1</f>
         <v/>
       </c>
       <c r="E5" t="inlineStr">
@@ -2511,7 +2532,7 @@
         <v>0.25</v>
       </c>
       <c r="D6" s="13">
-        <f>B6/Valuation!B29-1</f>
+        <f>B6/Valuation!B30-1</f>
         <v/>
       </c>
       <c r="E6" t="inlineStr">
@@ -2535,7 +2556,7 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>B7/Valuation!B29-1</f>
+        <f>B7/Valuation!B30-1</f>
         <v/>
       </c>
     </row>
@@ -2558,7 +2579,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0.08773255157812872</v>
+        <v>0.03721513270358695</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2594,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0.08773255157812872</v>
+        <v>0.03721513270358695</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2603,7 +2624,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>-2.099569464275375</v>
+        <v>-5.967697394530692</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
     </row>
@@ -2644,7 +2665,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.02196278349404875</v>
+        <v>0.0216394118621239</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>

--- a/nvidia/model.xlsx
+++ b/nvidia/model.xlsx
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>0.03</v>
+        <v>0.01845208816479593</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.032</v>
+        <v>0.02507125289887756</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.034</v>
+        <v>0.03169041763295919</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>0.035</v>
@@ -1437,22 +1437,22 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>2255844433.2256</v>
+        <v>1947960000</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>4159892889.371079</v>
+        <v>3276456990.413567</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>6927618817.01917</v>
+        <v>5663514683.839273</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>10180526745.58775</v>
+        <v>8803421410.69178</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>13667245149.23663</v>
+        <v>12290139814.34066</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>16588590319.25721</v>
+        <v>15739286869.89084</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>67.19058784732638</v>
+        <v>67.39430983648519</v>
       </c>
       <c r="C4" s="13" t="n">
         <v>0.25</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>197.1153741604705</v>
+        <v>197.3890110737761</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>0.5</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>437.1356049020856</v>
+        <v>437.4700917678697</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0.25</v>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0.03721513270358695</v>
+        <v>0.03905523917989117</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0.03721513270358695</v>
+        <v>0.03905523917989117</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>-5.967697394530692</v>
+        <v>-5.651189833929386</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
     </row>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.0216394118621239</v>
+        <v>0.02166849200301724</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>

--- a/nvidia/model.xlsx
+++ b/nvidia/model.xlsx
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>218.99</v>
+        <v>223.9</v>
       </c>
     </row>
   </sheetData>
@@ -2234,7 +2234,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Street figures are the consensus feed as retrieved 2026-08-05. Low/high are the support of published estimates, not a confidence interval.</t>
+          <t>Street figures are the consensus feed as retrieved 2026-08-07. Low/high are the support of published estimates, not a confidence interval.</t>
         </is>
       </c>
     </row>
@@ -2288,16 +2288,16 @@
         <v>380878301536</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>393421082449</v>
+        <v>393652880225</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>364137279674</v>
+        <v>364351823875</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>402545598372</v>
+        <v>402782772175</v>
       </c>
       <c r="F5" s="13" t="n">
-        <v>-0.0318813136167555</v>
+        <v>-0.03245137869103976</v>
       </c>
       <c r="G5" t="n">
         <v>40</v>
@@ -2316,16 +2316,16 @@
         <v>551876795946.3745</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>562864133910</v>
+        <v>563601060724</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>454422134234</v>
+        <v>455017083948</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>621815128083</v>
+        <v>622629236167</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>-0.01952040874820127</v>
+        <v>-0.02080241787083326</v>
       </c>
       <c r="G6" t="n">
         <v>40</v>
@@ -2344,16 +2344,16 @@
         <v>698958783499.2484</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>684573570460</v>
+        <v>686664195152</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>596685287724</v>
+        <v>596627356477</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>786109764326</v>
+        <v>786033442151</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.02101339236567701</v>
+        <v>0.01790480475616896</v>
       </c>
       <c r="G7" t="n">
         <v>27</v>
@@ -2375,10 +2375,10 @@
         <v>774228304289</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>646708625745</v>
+        <v>645938678105</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>886253376196</v>
+        <v>885198235337</v>
       </c>
       <c r="F8" s="13" t="n">
         <v>0.04034388660052146</v>
@@ -2403,16 +2403,16 @@
         <v>1005000000000</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>839470948392</v>
+        <v>838471504981</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1150416018302</v>
+        <v>1149046375062</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>-0.1417068210748231</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0.03905523917989117</v>
+        <v>0.006457311149012426</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0.03905523917989117</v>
+        <v>0.006457311149012426</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>-5.651189833929386</v>
+        <v>-37.96580511312897</v>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
     </row>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>41.8</v>
+        <v>27.29</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.02166849200301724</v>
+        <v>0.02145928366240926</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2751,7 +2751,7 @@
     <row r="5">
       <c r="A5" s="24" t="inlineStr">
         <is>
-          <t>Consensus estimates and price targets: FMP analyst/financial-estimates and analyst/price-target-consensus, retrieved 2026-08-05.</t>
+          <t>Consensus estimates and price targets: FMP analyst/financial-estimates and analyst/price-target-consensus, retrieved 2026-08-07.</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2768,7 @@
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
+          <t>YEAR-1 CAPEX ANCHOR. No capex guidance is published for this filer, so year 1 is $1.8bn reported plus 3 quarter(s) at the $1.8bn exit rate, giving $7.0bn.</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
         </is>
       </c>
     </row>
@@ -2787,6 +2787,16 @@
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>This is analytical research on public information. Not investment advice, not a recommendation to any person, and not a solicitation. Position sizing is illustrative against a notional $1bn book.</t>
         </is>

--- a/nvidia/model.xlsx
+++ b/nvidia/model.xlsx
@@ -2721,7 +2721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2778,7 +2778,7 @@
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
+          <t>YEAR-1 SEGMENT ANCHOR. No quarterly segment actuals are recorded for this filer, so year-1 segment revenue is checked only at the consolidated level.</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+          <t>DISCOUNT RATE. WACC is an input cell on Drivers and every discounted line references it, so changing it here re-values the model. It is worth knowing what that is worth: terminal value is 71% of enterprise value, the base case discounts at 9.75% giving $197.39, published third-party WACC estimates cluster near 7.57% giving $290.14, and the reverse DCF implies the market is discounting at 8.94%. The discount rate moves this valuation more than the depreciation schedule does.</t>
         </is>
       </c>
     </row>
@@ -2797,6 +2797,26 @@
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>This is analytical research on public information. Not investment advice, not a recommendation to any person, and not a solicitation. Position sizing is illustrative against a notional $1bn book.</t>
         </is>

--- a/nvidia/model.xlsx
+++ b/nvidia/model.xlsx
@@ -100,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -127,7 +127,6 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2431,7 +2430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2575,138 +2574,54 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Risk / reward</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="n">
-        <v>0.006457311149012426</v>
+          <t>Scenario expected value</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>224.9106059379768</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>long framing</t>
+          <t>illustrative probability-weighted arithmetic</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Payoff ratio b</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Position size</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0.006457311149012426</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>reward / risk</t>
+          <t>no capital recommendation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>p(win)</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>0.75</v>
+          <t>Binding constraint</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>implementation evidence missing</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>probability mass favouring the position</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Kelly f</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="n">
-        <v>-37.96580511312897</v>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>implementation inputs missing</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>Quarter-Kelly</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0.25 x Kelly</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>Liquidity cap</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>20% of ADV over 5 days</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Risk-budget cap</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>0.02145928366240926</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1.5% of NAV at risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Concentration cap</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>single-name hard limit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Position size</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>binding: quarter-Kelly</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Basis: illustrative $1bn book. Illustrative only.</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Basis: no capital recommendation; implementation inputs missing. Illustrative only.</t>
         </is>
       </c>
     </row>
@@ -2735,90 +2650,90 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>Base year: trailing twelve months to 2026-04-26, all statement inputs from SEC XBRL companyconcept (CIK 0001045810).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Quarterly series are reconstructed from filed facts: Q4 is derived as fiscal year minus the nine-month cumulative, and cash-flow items are unwound from year-to-date cumulatives.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>Consensus estimates and price targets: FMP analyst/financial-estimates and analyst/price-target-consensus, retrieved 2026-08-07.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>Segment revenue: FMP statements/revenue-product-segmentation. No SEC fallback exists because companyfacts flattens dimensioned facts; the segment sum is reconciled to consolidated revenue.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr"/>
+      <c r="A7" s="23" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>YEAR-1 CAPEX ANCHOR. No capex guidance is published for this filer, so year 1 is $1.8bn reported plus 3 quarter(s) at the $1.8bn exit rate, giving $7.0bn.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr"/>
+      <c r="A9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>YEAR-1 SEGMENT ANCHOR. No quarterly segment actuals are recorded for this filer, so year-1 segment revenue is checked only at the consolidated level.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr"/>
+      <c r="A11" s="23" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>DISCOUNT RATE. WACC is an input cell on Drivers and every discounted line references it, so changing it here re-values the model. It is worth knowing what that is worth: terminal value is 71% of enterprise value, the base case discounts at 9.75% giving $197.39, published third-party WACC estimates cluster near 7.57% giving $290.14, and the reverse DCF implies the market is discounting at 8.94%. The discount rate moves this valuation more than the depreciation schedule does.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr"/>
+      <c r="A13" s="23" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>MODEL DESIGN. We forecast EBITDA margin and derive EBIT by subtracting a depreciation schedule built from capex vintages. Forecasting EBIT margin directly hides the depreciation assumption.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr"/>
+      <c r="A15" s="23" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>KEY LIMITATION. The asset-life split driving the depreciation schedule is a stated assumption calibrated to reported D&amp;A, not a disclosed figure. It is the most load-bearing assumption in the model.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr"/>
+      <c r="A17" s="23" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
-        <is>
-          <t>This is analytical research on public information. Not investment advice, not a recommendation to any person, and not a solicitation. Position sizing is illustrative against a notional $1bn book.</t>
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>This is analytical research on public information. Not investment advice, not a recommendation to any person, and not a solicitation. No percentage sizing is provided without implementation and portfolio inputs.</t>
         </is>
       </c>
     </row>
